--- a/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Faustine va au jardin avec papa. Le lapin gris frotte son nez. Sa gamelle est vide. Faustine veut aider. Papa dit : on le fait ensemble. On est doux. Papa verse l'eau. Faustine tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Faustine pose la gamelle. Elle est douce. Sa main va lentement. Le lapin vient. Il boit. Il mange. Papa dit : on prend soin avec un adulte. On reste doux. Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.</t>
+          <t>Faustine va au jardin avec papa. Le lapin gris frotte son nez. Sa gamelle est vide. Faustine veut aider. On le fait ensemble. On est doux. Papa verse l'eau. Faustine tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Faustine pose la gamelle. Elle est douce. Sa main va lentement. Le lapin vient. Il boit. Il mange. On prend soin avec un adulte. On reste doux. Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine va au jardin avec papa. Le lapin gris frotte son nez. Sa gamelle est vide. Faustine veut aider.
+papa|On le fait ensemble. On est doux. Papa verse l'eau.
+narrateur|Faustine tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Faustine pose la gamelle. Elle est douce. Sa main va lentement. Le lapin vient. Il boit. Il mange.
+papa|On prend soin avec un adulte. On reste doux.
+narrateur|Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine donne l'eau au lapin. Comment fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Faustine a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le lapin croque encore. Faustine s'assoit près de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Faustine donne l'eau au lapin. Comment fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Faustine a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1839,7 @@
           <t>narrateur|Le lapin croque encore. Faustine s'assoit près de papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2007,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2050,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2265,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Faustine et l'eau du lapin</t>
+          <t>Le foin devant l'eau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut que le lapin boive. Le foin cache le biberon d'eau. Avec papa, ils écartent le foin. Le lapin boit.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Faustine va au jardin avec papa. Le lapin gris frotte son nez. Sa gamelle est vide. Faustine veut aider. On le fait ensemble. On est doux. Papa verse l'eau. Faustine tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Faustine pose la gamelle. Elle est douce. Sa main va lentement. Le lapin vient. Il boit. Il mange. On prend soin avec un adulte. On reste doux. Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.</t>
+          <t>Un rayon coupe le foin en paillettes. Les paillettes dansent, toutes d'or. Ça sent le champ coupé, et le bois sec. Le clapier a besoin d'air, Raphaël. Et d'eau. Je veux qu'il boive. On y va ensemble. Le chemin de dalles est chaud. Une abeille passe, sans s'arrêter. En ce moment, Raphaël est devant le clapier. Le lapin gris frotte son nez. Un tas de foin a glissé. Il cache le biberon d'eau. Je ne vois plus l'eau. Le foin est passé devant. On écarte, tout doux. Avec un adulte. Tu prends le foin avec moi ? Oui, papa. Raphaël pince une poignée. Le foin pique un peu les doigts. Papa pince l'autre côté. Ils posent le foin plus loin, dans le râtelier. Le biberon réapparaît. Il est presque vide. Presque plus d'eau. On remplit. Tout doux. Raphaël tient le biberon avec papa. Le robinet du jardin chante. L'eau monte, pas trop. On referme. Ils recrochent le biberon. La main de Raphaël va lentement. Une goutte apparaît au goulot. On recule. On reste près de moi. Le lapin s'approche. Il lape la goutte. Il boit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Faustine va au jardin &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa. Le lapin gris frotte son nez. Sa gamelle est vide. Faustine veut aider. Papa dit : on le fait ensemble. On est doux. Papa verse l'eau. Faustine tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Faustine pose la gamelle. Elle est douce. Sa main va lentement. Le lapin vient. Il boit. Il mange. Papa dit : on prend soin avec un adulte. On reste doux. Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon coupe le foin en paillettes. Les paillettes dansent, toutes d'or. Ça sent le champ coupé, et le bois sec. Le clapier a besoin d'air, Raphaël. Et d'eau. Je veux qu'il boive. On y va ensemble. Le chemin de dalles est chaud. Une abeille passe, sans s'arrêter. En ce moment, Raphaël est devant le clapier. Le lapin gris frotte son nez. Un tas de foin a glissé. Il cache le biberon d'eau. Je ne vois plus l'eau. Le foin est passé devant. On écarte, tout doux. Avec un adulte. Tu prends le foin avec moi ? Oui, papa. Raphaël pince une poignée. Le foin pique un peu les doigts. Papa pince l'autre côté. Ils posent le foin plus loin, dans le râtelier. Le biberon réapparaît. Il est presque vide. Presque plus d'eau. On remplit. Tout doux. Raphaël tient le biberon avec papa. Le robinet du jardin chante. L'eau monte, pas trop. On referme. Ils recrochent le biberon. La main de Raphaël va lentement. Une goutte apparaît au goulot. On recule. On reste près de moi. Le lapin s'approche. Il lape la goutte. Il boit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Faustine va au jardin avec papa. Le lapin gris frotte son nez. Sa gamelle est vide. Faustine veut aider.
-papa|On le fait ensemble. On est doux. Papa verse l'eau.
-narrateur|Faustine tient le bol avec papa. L'eau arrive tout doucement. Papa met des croquettes. Faustine pose la gamelle. Elle est douce. Sa main va lentement. Le lapin vient. Il boit. Il mange.
-papa|On prend soin avec un adulte. On reste doux.
-narrateur|Faustine caresse le dos, tout doux. Le lapin croque. Faustine sourit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un rayon coupe le foin en paillettes.
+narrateur|Les paillettes dansent, toutes d'or.
+narrateur|Ça sent le champ coupé, et le bois sec.
+papa|Le clapier a besoin d'air, Raphaël.
+enfant-m|Et d'eau.
+enfant-m|Je veux qu'il boive.
+papa|On y va ensemble.
+narrateur|Le chemin de dalles est chaud.
+narrateur|Une abeille passe, sans s'arrêter.
+narrateur|En ce moment, Raphaël est devant le clapier.
+narrateur|Le lapin gris frotte son nez.
+narrateur|Un tas de foin a glissé.
+narrateur|Il cache le biberon d'eau.
+enfant-m|Je ne vois plus l'eau.
+papa|Le foin est passé devant.
+papa|On écarte, tout doux.
+papa|Avec un adulte.
+papa|Tu prends le foin avec moi ?
+enfant-m|Oui, papa.
+narrateur|Raphaël pince une poignée.
+narrateur|Le foin pique un peu les doigts.
+narrateur|Papa pince l'autre côté.
+narrateur|Ils posent le foin plus loin, dans le râtelier.
+narrateur|Le biberon réapparaît.
+narrateur|Il est presque vide.
+enfant-m|Presque plus d'eau.
+papa|On remplit.
+papa|Tout doux.
+narrateur|Raphaël tient le biberon avec papa.
+narrateur|Le robinet du jardin chante.
+narrateur|L'eau monte, pas trop.
+papa|On referme.
+narrateur|Ils recrochent le biberon.
+narrateur|La main de Raphaël va lentement.
+narrateur|Une goutte apparaît au goulot.
+papa|On recule.
+papa|On reste près de moi.
+narrateur|Le lapin s'approche.
+narrateur|Il lape la goutte.
+enfant-m|Il boit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1390,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Faustine donne l'eau au lapin. Comment fait-elle ?</t>
+          <t>Raphaël donne l'eau au lapin. Comment fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Faustine donne l'eau au lapin. Comment fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël donne l'eau au lapin. Comment fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1359,12 +1405,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>douce</t>
+          <t>doux</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>douce | doux | avec papa | avec un adulte</t>
+          <t>doux | douce | avec papa | avec un adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle est douce, avec papa. Comment fait Faustine ?</t>
+          <t>Il est doux, avec papa. Comment fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1474,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1546,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Faustine donne l'eau au lapin. Comment fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Raphaël donne l'eau au lapin.
+narrateur|Comment fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Faustine a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
+          <t>Le lapin boit encore, tout calme. Ses oreilles vont, viennent. Le foin cachait tout. Oui. Tu as été doux. Avec un adulte. Merci, Raphaël. Tu as vu les paillettes ? Elles dansaient. Le foin, maintenant, est à sa place. Raphaël pose une poignée dans le râtelier. Pas devant l'eau. Il ne prend pas le lapin. Ses mains sentent le champ. Ça pique encore. On se rince au robinet ? Oui. L'eau du jardin est fraîche. Elle enlève les paillettes. Le lapin a de l'eau. Et du foin, à côté.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Faustine a été douce. Elle a versé l'eau &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lapin boit encore, tout calme. Ses oreilles vont, viennent. Le foin cachait tout. Oui. Tu as été doux. Avec un adulte. Merci, Raphaël. Tu as vu les paillettes ? Elles dansaient. Le foin, maintenant, est à sa place. Raphaël pose une poignée dans le râtelier. Pas devant l'eau. Il ne prend pas le lapin. Ses mains sentent le champ. Ça pique encore. On se rince au robinet ? Oui. L'eau du jardin est fraîche. Elle enlève les paillettes. Le lapin a de l'eau. Et du foin, à côté.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1642,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1718,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Faustine a été douce. Elle a versé l'eau avec un adulte. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lapin boit encore, tout calme.
+narrateur|Ses oreilles vont, viennent.
+enfant-m|Le foin cachait tout.
+papa|Oui.
+papa|Tu as été doux.
+papa|Avec un adulte.
+papa|Merci, Raphaël.
+papa|Tu as vu les paillettes ?
+enfant-m|Elles dansaient.
+papa|Le foin, maintenant, est à sa place.
+narrateur|Raphaël pose une poignée dans le râtelier.
+narrateur|Pas devant l'eau.
+narrateur|Il ne prend pas le lapin.
+narrateur|Ses mains sentent le champ.
+enfant-m|Ça pique encore.
+papa|On se rince au robinet ?
+enfant-m|Oui.
+narrateur|L'eau du jardin est fraîche.
+narrateur|Elle enlève les paillettes.
+enfant-m|Le lapin a de l'eau.
+papa|Et du foin, à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le lapin croque encore. Faustine s'assoit près de papa.</t>
+          <t>Le rayon a bougé. Il touche maintenant le biberon. L'eau dedans fait un petit or. Ça brille. Il a bu. C'était ça, ton envie. Le lapin croque une tige. Puis il revient à la goutte. Foin, et eau. Les deux. Raphaël s'assoit sur la dalle chaude. Papa s'assoit près de lui. Une paillette reste sur le genou. On la souffle ? Oui. La paillette s'en va, toute légère.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le lapin croque encore. Faustine s'assoit près de papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rayon a bougé. Il touche maintenant le biberon. L'eau dedans fait un petit or. Ça brille. Il a bu. C'était ça, ton envie. Le lapin croque une tige. Puis il revient à la goutte. Foin, et eau. Les deux. Raphaël s'assoit sur la dalle chaude. Papa s'assoit près de lui. Une paillette reste sur le genou. On la souffle ? Oui. La paillette s'en va, toute légère.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1833,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1836,10 +1901,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le lapin croque encore. Faustine s'assoit près de papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le rayon a bougé.
+narrateur|Il touche maintenant le biberon.
+narrateur|L'eau dedans fait un petit or.
+enfant-m|Ça brille.
+papa|Il a bu.
+papa|C'était ça, ton envie.
+narrateur|Le lapin croque une tige.
+narrateur|Puis il revient à la goutte.
+papa|Foin, et eau.
+enfant-m|Les deux.
+narrateur|Raphaël s'assoit sur la dalle chaude.
+narrateur|Papa s'assoit près de lui.
+narrateur|Une paillette reste sur le genou.
+papa|On la souffle ?
+enfant-m|Oui.
+narrateur|La paillette s'en va, toute légère.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1864,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le biberon n'est plus caché. Le lapin trouve l'eau. Le foin sent encore le champ. Le jardin redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le biberon n'est plus caché. Le lapin trouve l'eau. Le foin sent encore le champ. Le jardin redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1925,14 +2004,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2004,10 +2083,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Le biberon n'est plus caché.
+papa|Le lapin trouve l'eau.
+narrateur|Le foin sent encore le champ.
+narrateur|Le jardin redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2064,6 +2145,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, clapier, poussière de foin dans le soleil</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Faustine, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
